--- a/liste prix ventes articles part3.xlsx
+++ b/liste prix ventes articles part3.xlsx
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="154">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="159">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="170">
@@ -12850,7 +12850,7 @@
         </is>
       </c>
       <c r="C829" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="830">
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="909">
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="C910" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="911">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="C911" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="912">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>LAIT HYDRATANT LANA PALMERA 250ML</t>
+          <t>LAIT HYDRATANT LANA PALMERA ASS 250ML</t>
         </is>
       </c>
       <c r="C913" t="n">
@@ -28651,7 +28651,7 @@
         </is>
       </c>
       <c r="C1883" t="n">
-        <v>850</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1884">
@@ -29386,7 +29386,7 @@
         </is>
       </c>
       <c r="C1932" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1933">
@@ -29416,7 +29416,7 @@
         </is>
       </c>
       <c r="C1934" t="n">
-        <v>2500</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="1935">
@@ -29431,7 +29431,7 @@
         </is>
       </c>
       <c r="C1935" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="1936">
@@ -29461,7 +29461,7 @@
         </is>
       </c>
       <c r="C1937" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="1938">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="C1939" t="n">
-        <v>2500</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1940">
@@ -29506,7 +29506,7 @@
         </is>
       </c>
       <c r="C1940" t="n">
-        <v>3000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1941">
@@ -29536,7 +29536,7 @@
         </is>
       </c>
       <c r="C1942" t="n">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="1943">
